--- a/sample_data/06_资质数据库参考材料/资质材料清单.xlsx
+++ b/sample_data/06_资质数据库参考材料/资质材料清单.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -539,22 +539,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>铁路工程施工总承包一级</t>
+          <t>电子与智能化工程专业承包壹级</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>企业资质_铁路总承包一级_20301231.docx</t>
+          <t>企业资质_电子智能化壹级_20291219.docx</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2028-07-20</t>
+          <t>2027-09-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>铁路工程施工总承包一级</t>
+          <t>电子与智能化工程专业承包壹级</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>企业资质_安全生产许可证_20281231.docx</t>
+          <t>企业资质_安全生产许可证_20290604.docx</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2027-07-21</t>
+          <t>2027-09-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -649,17 +649,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>京沪高铁XX段合同</t>
+          <t>地铁12号线电气火灾监控中标</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>业绩_京沪高铁XX段合同_2024.docx</t>
+          <t>业绩_地铁12号线中标通知_2025.docx</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>XX铁路局</t>
+          <t>中铁电气化局</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>京沪高铁XX段合同</t>
+          <t>地铁12号线电气火灾监控中标</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,17 +704,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>地铁XX号线中标通知书</t>
+          <t>龙烟铁路RTU采购合同</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>业绩_地铁XX号线中标通知_2023.docx</t>
+          <t>业绩_龙烟铁路RTU合同_2024.docx</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>XX地铁集团</t>
+          <t>中铁四局电气化公司</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>地铁XX号线中标通知书</t>
+          <t>龙烟铁路RTU采购合同</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -759,27 +759,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>项目经理简历及建造师证</t>
+          <t>项目经理张方恒简历</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>人员_项目经理张三_建造师.docx</t>
+          <t>人员_项目经理张方恒.docx</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2027-07-21</t>
+          <t>2027-09-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>住建部</t>
+          <t>企业内部</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>项目经理简历及建造师证</t>
+          <t>项目经理张方恒简历</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>人员_技术负责人李某某_职称.docx</t>
+          <t>人员_技术负责人职称.docx</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2027-07-21</t>
+          <t>2027-09-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2027-07-21</t>
+          <t>2027-09-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
